--- a/public/calculadora-ir-configuracoes.xlsx
+++ b/public/calculadora-ir-configuracoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thais Camilo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83ED0AF5-013E-403B-8F41-ECFC21152E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8DDD737-3A97-4953-9478-41F85FC87EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
     <t>Regra_Dividendos</t>
   </si>
   <si>
-    <t>PL 1087/25</t>
+    <t>PL 1087/26</t>
   </si>
   <si>
     <t>Baseada no PL 1087/25 que prevê taxação de altas rendas.</t>
@@ -765,7 +765,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>189.59</v>
+        <v>289.58999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -773,7 +773,7 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <v>50000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -789,7 +789,7 @@
         <v>26</v>
       </c>
       <c r="B5">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="6" spans="1:4">

--- a/public/calculadora-ir-configuracoes.xlsx
+++ b/public/calculadora-ir-configuracoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thais Camilo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13BDF378-4A7A-4F69-B7B9-F2C86FE98611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61B373AF-DA11-4F53-AECE-3F2A7790ABB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,7 +127,7 @@
     <t>Regra_Dividendos</t>
   </si>
   <si>
-    <t>PL 1087/25</t>
+    <t>PL 1087/29</t>
   </si>
   <si>
     <t>Baseada no PL 1087/25 que prevê taxação de altas rendas.</t>
@@ -768,7 +768,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>5000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -776,7 +776,7 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <v>189.59</v>
+        <v>289.58999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -784,7 +784,7 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>50000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -792,7 +792,7 @@
         <v>26</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -800,7 +800,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="7" spans="1:4">

--- a/public/calculadora-ir-configuracoes.xlsx
+++ b/public/calculadora-ir-configuracoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thais Camilo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61B373AF-DA11-4F53-AECE-3F2A7790ABB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04056DFF-8538-4284-AD69-F28FE1A5E680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,7 +127,7 @@
     <t>Regra_Dividendos</t>
   </si>
   <si>
-    <t>PL 1087/29</t>
+    <t>PL 1087/25</t>
   </si>
   <si>
     <t>Baseada no PL 1087/25 que prevê taxação de altas rendas.</t>
@@ -768,7 +768,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>4000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -776,7 +776,7 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <v>289.58999999999997</v>
+        <v>189.59</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -784,7 +784,7 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>60000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -792,7 +792,7 @@
         <v>26</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -800,7 +800,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="7" spans="1:4">

--- a/public/calculadora-ir-configuracoes.xlsx
+++ b/public/calculadora-ir-configuracoes.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thais Camilo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04056DFF-8538-4284-AD69-F28FE1A5E680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3ED6B537-4534-408A-BCC2-740FFF625043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Calculadora IRPF 2026" sheetId="1" r:id="rId1"/>
-    <sheet name="tabelas_referencia" sheetId="2" r:id="rId2"/>
-    <sheet name="parametros_gerais" sheetId="3" r:id="rId3"/>
+    <sheet name="Simulador IRPF 2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabela de Referencia 2026" sheetId="2" r:id="rId2"/>
+    <sheet name="tabelas_referencia" sheetId="4" r:id="rId3"/>
+    <sheet name="parametros_gerais" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,51 +39,162 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
-  <si>
-    <t>CALCULADORA IRPF 2026 (INCLUINDO ADICIONAL 10%)</t>
-  </si>
-  <si>
-    <t>Rendimentos Tributáveis (Salário/Pró-labore):</t>
-  </si>
-  <si>
-    <t>Lucros e Dividendos Recebidos:</t>
-  </si>
-  <si>
-    <t>Quantidade de dependentes (R$ 189,59 cada):</t>
-  </si>
-  <si>
-    <t>Outras Deduções (Previdência, etc):</t>
-  </si>
-  <si>
-    <t>DETALHAMENTO DO IMPOSTO</t>
-  </si>
-  <si>
-    <t>Base de Cálculo IRPF (Tributáveis - Deduções):</t>
-  </si>
-  <si>
-    <t>1. IRPF Progressivo (Sobre Tributáveis):</t>
-  </si>
-  <si>
-    <t>2. Adicional de 10% (Excedente a R$ 50k):</t>
-  </si>
-  <si>
-    <t>TOTAL DE IMPOSTO A PAGAR:</t>
-  </si>
-  <si>
-    <t>RENDA LÍQUIDA MENSAL:</t>
-  </si>
-  <si>
-    <t>Observações:</t>
-  </si>
-  <si>
-    <t>1. Tabela IRPF 2026: Considera a isenção de R$ 5.000,00 (projeção).</t>
-  </si>
-  <si>
-    <t>2. Adicional 10%: Aplicado sobre a renda total (tributável + dividendos) que exceder R$ 50.000,00.</t>
-  </si>
-  <si>
-    <t>3. Regra de Dividendos: Baseada no PL 1087/25 que prevê taxação de altas rendas.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="71">
+  <si>
+    <t>Simulador do Imposto de Renda Pessoa Física (IRPF 2026)</t>
+  </si>
+  <si>
+    <t>Calculadora mensal interativa com comparação da Opção Mais Favorável (Dedução Simplificada de R$ 607,20 vs. Deduções Legais)</t>
+  </si>
+  <si>
+    <t>1. DADOS DE ENTRADA (MENSAL)</t>
+  </si>
+  <si>
+    <t>Item / Parâmetro</t>
+  </si>
+  <si>
+    <t>Valor Informado</t>
+  </si>
+  <si>
+    <t>Unidade / Nota</t>
+  </si>
+  <si>
+    <t>Rendimento Salarial / Pró-Labore Bruto</t>
+  </si>
+  <si>
+    <t>R$</t>
+  </si>
+  <si>
+    <t>Desconto INSS Oficial / Previdência Oficial</t>
+  </si>
+  <si>
+    <t>Número de Dependentes (R$ 189,59 cada)</t>
+  </si>
+  <si>
+    <t>unidades</t>
+  </si>
+  <si>
+    <t>Outras Deduções Legais Mensais (Pensão Alimentícia, etc.)</t>
+  </si>
+  <si>
+    <t>Distribuição de Lucros e Dividendos Recebidos no Mês</t>
+  </si>
+  <si>
+    <t>2. APURAÇÃO DA BASE DE CÁLCULO MAIS FAVORÁVEL</t>
+  </si>
+  <si>
+    <t>Opção de Dedução</t>
+  </si>
+  <si>
+    <t>Regra de Abatimento</t>
+  </si>
+  <si>
+    <t>Base de Cálculo Resultante (R$)</t>
+  </si>
+  <si>
+    <t>Dedução Total pelas Regras Legais</t>
+  </si>
+  <si>
+    <t>INSS + Dependentes + Pensão</t>
+  </si>
+  <si>
+    <t>Base de Cálculo (Deduções Legais)</t>
+  </si>
+  <si>
+    <t>Rendimento Bruto − Deduções Legais Totais</t>
+  </si>
+  <si>
+    <t>Base de Cálculo (Desconto Simplificado Mensal - R$ 607,20)</t>
+  </si>
+  <si>
+    <t>Rendimento Bruto − Desconto Simplificado (R$ 607,20)</t>
+  </si>
+  <si>
+    <t>BASE DE CÁLCULO MAIS FAVORÁVEL (MENOR VALOR)</t>
+  </si>
+  <si>
+    <t>IF(D16&lt;=D17, "Deduções Legais", "Desconto Simplificado")</t>
+  </si>
+  <si>
+    <t>3. CÁLCULO DO IMPOSTO DE RENDA FINAL</t>
+  </si>
+  <si>
+    <t>Etapa de Cálculo</t>
+  </si>
+  <si>
+    <t>Fórmula / Regra Aplicada</t>
+  </si>
+  <si>
+    <t>Valor Resultante (R$)</t>
+  </si>
+  <si>
+    <t>Alíquota da Tabela Progressiva</t>
+  </si>
+  <si>
+    <t>Conforme faixa da base de cálculo</t>
+  </si>
+  <si>
+    <t>Dedução da Tabela Progressiva</t>
+  </si>
+  <si>
+    <t>Parcela a deduzir da tabela</t>
+  </si>
+  <si>
+    <t>Imposto Bruto Devido (Tabela Padrão)</t>
+  </si>
+  <si>
+    <t>Base de Cálculo x Alíquota − Parcela a Deduzir</t>
+  </si>
+  <si>
+    <t>Redutor da Nova Lei (Isenção R$ 5k / Transição)</t>
+  </si>
+  <si>
+    <t>Redução para renda até R$ 7.350,00</t>
+  </si>
+  <si>
+    <t>Imposto Final sobre Salário/Pró-Labore</t>
+  </si>
+  <si>
+    <t>Imposto Efetivo de Renda no Mês</t>
+  </si>
+  <si>
+    <t>Imposto de Renda sobre Lucros/Dividendos (10%)</t>
+  </si>
+  <si>
+    <t>10% sobre o excedente de R$ 50.000/mês</t>
+  </si>
+  <si>
+    <t>IMPOSTO DE RENDA TOTAL A PAGAR NO MÊS</t>
+  </si>
+  <si>
+    <t>Soma: IR Salário + IR Lucros/Dividendos</t>
+  </si>
+  <si>
+    <t>Tabela Progressiva Mensal do IRPF (2026)</t>
+  </si>
+  <si>
+    <t>Faixa de Rendimento Tributável (R$)</t>
+  </si>
+  <si>
+    <t>Alíquota</t>
+  </si>
+  <si>
+    <t>Parcela a Deduzir do Imposto (R$)</t>
+  </si>
+  <si>
+    <t>Até R$ 2.428,80</t>
+  </si>
+  <si>
+    <t>De R$ 2.428,81 até R$ 2.826,65</t>
+  </si>
+  <si>
+    <t>De R$ 2.826,66 até R$ 3.751,05</t>
+  </si>
+  <si>
+    <t>De R$ 3.751,06 até R$ 4.664,68</t>
+  </si>
+  <si>
+    <t>Acima de R$ 4.664,68</t>
   </si>
   <si>
     <t>Faixa</t>
@@ -110,6 +222,15 @@
   </si>
   <si>
     <t>Teto_Isencao</t>
+  </si>
+  <si>
+    <t>Renda mensal até onde o imposto é zerado</t>
+  </si>
+  <si>
+    <t>Isencao_Fase_Out</t>
+  </si>
+  <si>
+    <t>Renda até onde o desconto é aplicado progressivamente</t>
   </si>
   <si>
     <t>Deducao_Dependente</t>
@@ -137,10 +258,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;R$ &quot;#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,8 +272,30 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color rgb="FF375623"/>
+      <sz val="16"/>
+      <color rgb="FF1B365D"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1B365D"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -160,10 +304,10 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -172,7 +316,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,8 +325,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FF1B365D"/>
+        <bgColor rgb="FF1B365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor rgb="FFF8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF5"/>
+        <bgColor rgb="FFE8EEF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -196,16 +364,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -213,17 +381,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,122 +728,258 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="B2:D28"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="39.42578125" customWidth="1"/>
-    <col min="2" max="3" width="20" customWidth="1"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.600000000000001">
-      <c r="A1" s="1" t="s">
+    <row r="2" spans="2:4" ht="21">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+    <row r="3" spans="2:4">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
-        <v>50000.01</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+    </row>
+    <row r="5" spans="2:4" ht="15.6">
+      <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="6">
+        <v>5500</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="D8" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="21">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="6">
-        <f>MAX(0, B3 - (B5 * 189.59) - B6)</f>
-        <v>49620.83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="5" t="s">
+      <c r="D9" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="6">
-        <f>IF(B9&lt;=5000, 0, IF(B9&lt;=6000, B9*0.075-375, IF(B9&lt;=7500, B9*0.15-825, IF(B9&lt;=9000, B9*0.225-1387.5, B9*0.275-1837.5))))</f>
-        <v>11808.228250000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7">
-        <f>MAX(0, (B3 + B4 - 50000) * 0.1)</f>
-        <v>1.0000000002037268E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="8">
-        <f>B10 + B11</f>
-        <v>11808.229250000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="8">
-        <f>(B3 + B4) - B13</f>
-        <v>38191.780749999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
+      <c r="C11" s="6">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="15.6">
+      <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
+    <row r="14" spans="2:4">
+      <c r="B14" s="4" t="s">
         <v>14</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="9">
+        <f>C8 + (C9 * 189.59) + C10</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="10">
+        <f>MAX(0, C7 - C15)</f>
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="10">
+        <f>MAX(0, C7 - 607.2)</f>
+        <v>4892.8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="13">
+        <f>MIN(D16, D17)</f>
+        <v>4892.8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="15.6">
+      <c r="B20" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="14">
+        <f>IF(D18&lt;=2428.8, 0, IF(D18&lt;=2826.65, 0.075, IF(D18&lt;=3751.05, 0.15, IF(D18&lt;=4664.68, 0.225, 0.275))))</f>
+        <v>0.27500000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="10">
+        <f>IF(D18&lt;=2428.8, 0, IF(D18&lt;=2826.65, 182.16, IF(D18&lt;=3751.05, 394.16, IF(D18&lt;=4664.68, 675.49, 908.73))))</f>
+        <v>908.73</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="10">
+        <f>MAX(0, D18*D22 - D23)</f>
+        <v>436.79000000000019</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="10">
+        <f>IF(C7&lt;=5000, D24, IF(C7&lt;=7350, MAX(0, 978.62 - (0.133145 * C7)), 0))</f>
+        <v>246.32249999999988</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="16">
+        <f>MAX(0, D24 - D25)</f>
+        <v>190.46750000000031</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="10">
+        <f>IF(C11&gt;50000, (C11 - 50000)*0.1, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="19">
+        <f>D26 + D27</f>
+        <v>190.46750000000031</v>
       </c>
     </row>
   </sheetData>
@@ -650,92 +988,186 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0B86D7-99F9-482A-8E8D-B4195C7E225C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="32" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" ht="21">
+      <c r="B2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="20">
+        <v>0</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="20">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="D6" s="10">
+        <v>182.16</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="D7" s="10">
+        <v>394.16</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="20">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="D8" s="10">
+        <v>675.49</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="20">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="D9" s="10">
+        <v>908.73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B869F42E-A2D3-4E24-9CDB-93E6D826ACA5}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="22">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22">
+        <v>2428.8000000000002</v>
+      </c>
+      <c r="C2" s="22">
+        <v>0</v>
+      </c>
+      <c r="D2" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="22">
+        <v>2</v>
+      </c>
+      <c r="B3" s="22">
+        <v>2826.65</v>
+      </c>
+      <c r="C3" s="22">
+        <v>7.5</v>
+      </c>
+      <c r="D3" s="22">
+        <v>182.16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="22">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22">
+        <v>3751.05</v>
+      </c>
+      <c r="C4" s="22">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5000</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>6000</v>
-      </c>
-      <c r="C3">
-        <v>7.5</v>
-      </c>
-      <c r="D3">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>7500</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
-      <c r="D4">
-        <v>825</v>
+      <c r="D4" s="22">
+        <v>394.16</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5">
+      <c r="A5" s="22">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>9000</v>
-      </c>
-      <c r="C5">
+      <c r="B5" s="22">
+        <v>4664.68</v>
+      </c>
+      <c r="C5" s="22">
         <v>22.5</v>
       </c>
-      <c r="D5">
-        <v>1387.5</v>
+      <c r="D5" s="22">
+        <v>675.49</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6">
+      <c r="A6" s="22">
         <v>5</v>
       </c>
-      <c r="C6">
+      <c r="B6" s="22">
+        <v>999999999</v>
+      </c>
+      <c r="C6" s="22">
         <v>27.5</v>
       </c>
-      <c r="D6">
-        <v>1837.5</v>
+      <c r="D6" s="22">
+        <v>908.74</v>
       </c>
     </row>
   </sheetData>
@@ -743,75 +1175,102 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC854036-FFB5-45DC-AD7A-84466E74F51B}">
-  <dimension ref="A1:D7"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C422EF-16AD-4D31-8115-80C20ACB3E96}">
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" t="s">
-        <v>22</v>
+      <c r="A1" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2">
+      <c r="A2" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="22">
         <v>5000</v>
       </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3">
+      <c r="A3" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="22">
+        <v>7350</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="22">
         <v>189.59</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4">
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="22">
         <v>50000</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5">
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="22">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6">
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="22">
         <v>2026</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/public/calculadora-ir-configuracoes.xlsx
+++ b/public/calculadora-ir-configuracoes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thais Camilo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1A8117A-F23C-4DC0-82BA-EC052AE73D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EA77541-335D-4732-97BE-ED41ABA3AAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Simulador IRPF 2026" sheetId="1" r:id="rId1"/>
@@ -1173,7 +1173,7 @@
         <v>27.5</v>
       </c>
       <c r="D6" s="22">
-        <v>908.74</v>
+        <v>908.73</v>
       </c>
     </row>
   </sheetData>
